--- a/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
+++ b/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFF510D5-EE91-4EF3-AAF9-C1EFE4A4D236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7BF57D4-A2CE-4CF4-A116-A03348C05492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="13" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="12" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="11" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="10" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="9" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="18" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="17" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="16" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="15" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="14" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1355,7 +1355,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC38F6D8-5D10-AFFE-AA71-7E5AC7F55D06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83CB6552-4958-78FE-C85B-B49ED57B2A3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,7 +1706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923098B9-3DF3-495C-8C56-ABCFC77DB7AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FBA0821-A763-40A8-9636-100D7FD14568}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4834,7 +4834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF38D22F-0DEB-43C6-9A85-F78B914DC17C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064890E8-E764-4F69-B2E9-E93B41E260F6}">
   <dimension ref="B2:L32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5899,7 +5899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A20A42-A06B-4C70-8E27-5502EE2F8810}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D63B7B9-50E6-42FF-80E0-6302A62AFECB}">
   <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6378,7 +6378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1C4E7-C201-4533-A9F2-23DB19CE7613}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D535EE-A4D0-45FF-BA4D-28B2CDD674C2}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6929,7 +6929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE663B4-3731-4A35-BF81-21ED3B0E88DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BAB8885-1E8E-455E-B000-8806284E9C54}">
   <dimension ref="A1:AD156"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
+++ b/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7BF57D4-A2CE-4CF4-A116-A03348C05492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9010F27F-76BF-40B5-8F5E-2DF58F51EF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="18" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="17" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="16" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="15" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="14" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1355,7 +1355,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83CB6552-4958-78FE-C85B-B49ED57B2A3D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8968E7B-8077-2849-3750-4BD6CFCF78F0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,7 +1706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FBA0821-A763-40A8-9636-100D7FD14568}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F815613-45DB-46E2-A150-AE30AA914683}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4834,7 +4834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064890E8-E764-4F69-B2E9-E93B41E260F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4692E1-8D3F-4392-8882-429DEA8B53F7}">
   <dimension ref="B2:L32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5899,7 +5899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D63B7B9-50E6-42FF-80E0-6302A62AFECB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489DE2A2-BB67-48A4-B2B3-3B8B57264BD3}">
   <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6378,7 +6378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D535EE-A4D0-45FF-BA4D-28B2CDD674C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B70F7C-DEC0-4028-8F88-CEA826044BC0}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6929,7 +6929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BAB8885-1E8E-455E-B000-8806284E9C54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D740BB8-E11A-45A8-9C2C-E6B2EF7CD10D}">
   <dimension ref="A1:AD156"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14820,7 +14820,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T132">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451533</v>
       </c>
       <c r="U132">
         <v>0</v>
@@ -14867,7 +14867,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T133">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451533</v>
       </c>
       <c r="U133">
         <v>0</v>
@@ -14914,7 +14914,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T134">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451533</v>
       </c>
       <c r="U134">
         <v>0</v>

--- a/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
+++ b/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9010F27F-76BF-40B5-8F5E-2DF58F51EF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16E1F127-EF12-4BB5-B40C-9ECF16AD71CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="28" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="27" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="26" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="25" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="24" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1355,7 +1355,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8968E7B-8077-2849-3750-4BD6CFCF78F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A0DEC2D-D45A-677A-5529-FBEE84DB4910}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,7 +1706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F815613-45DB-46E2-A150-AE30AA914683}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40BF1F7-B1A3-4DB2-A6F7-844817EA65A9}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4834,7 +4834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4692E1-8D3F-4392-8882-429DEA8B53F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF3E47D-EB67-48C3-9F28-37135E97712B}">
   <dimension ref="B2:L32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5899,7 +5899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489DE2A2-BB67-48A4-B2B3-3B8B57264BD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6344CC7-48EC-4157-81ED-787E395C1769}">
   <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6378,7 +6378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B70F7C-DEC0-4028-8F88-CEA826044BC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F215931-7F5E-4B1C-A5D5-D4071506A5E4}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6929,7 +6929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D740BB8-E11A-45A8-9C2C-E6B2EF7CD10D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3CDA99-07A8-45D2-9C12-36A4E6AFF60D}">
   <dimension ref="A1:AD156"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12437,7 +12437,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T91">
-        <v>0.17882039730553978</v>
+        <v>0.17882039730553981</v>
       </c>
       <c r="U91">
         <v>0</v>
@@ -12484,7 +12484,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T92">
-        <v>0.17882039730553978</v>
+        <v>0.17882039730553981</v>
       </c>
       <c r="U92">
         <v>0</v>
@@ -12531,7 +12531,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T93">
-        <v>0.17882039730553978</v>
+        <v>0.17882039730553981</v>
       </c>
       <c r="U93">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T132">
-        <v>0.17225936902451533</v>
+        <v>0.17225936902451539</v>
       </c>
       <c r="U132">
         <v>0</v>
@@ -14867,7 +14867,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T133">
-        <v>0.17225936902451533</v>
+        <v>0.17225936902451539</v>
       </c>
       <c r="U133">
         <v>0</v>
@@ -14914,7 +14914,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T134">
-        <v>0.17225936902451533</v>
+        <v>0.17225936902451539</v>
       </c>
       <c r="U134">
         <v>0</v>

--- a/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
+++ b/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16E1F127-EF12-4BB5-B40C-9ECF16AD71CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BCE4CE5-3EB7-4ECD-9ECC-BADC3007DDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="28" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="27" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="26" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="25" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="24" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="33" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="32" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="31" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="30" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="29" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1355,7 +1355,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A0DEC2D-D45A-677A-5529-FBEE84DB4910}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDF0A48E-E3A2-C644-D277-9B3B3B8E5B1F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,7 +1706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40BF1F7-B1A3-4DB2-A6F7-844817EA65A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F4BF8C-7A3A-4A0E-AA8A-E40EDD42D901}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4834,7 +4834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF3E47D-EB67-48C3-9F28-37135E97712B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B6B2DC-7AA2-4683-93BE-8AA1E7946C22}">
   <dimension ref="B2:L32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5899,7 +5899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6344CC7-48EC-4157-81ED-787E395C1769}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B97B84-2BB9-4C43-8E2B-286EDCB0E01E}">
   <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6378,7 +6378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F215931-7F5E-4B1C-A5D5-D4071506A5E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858B4A8C-D1C5-4A81-B199-5A877F0BFBF8}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6929,7 +6929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3CDA99-07A8-45D2-9C12-36A4E6AFF60D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1BD937-FFD3-4BCC-9992-276769939549}">
   <dimension ref="A1:AD156"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12437,7 +12437,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T91">
-        <v>0.17882039730553981</v>
+        <v>0.17882039730553978</v>
       </c>
       <c r="U91">
         <v>0</v>
@@ -12484,7 +12484,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T92">
-        <v>0.17882039730553981</v>
+        <v>0.17882039730553978</v>
       </c>
       <c r="U92">
         <v>0</v>
@@ -12531,7 +12531,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T93">
-        <v>0.17882039730553981</v>
+        <v>0.17882039730553978</v>
       </c>
       <c r="U93">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T132">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451541</v>
       </c>
       <c r="U132">
         <v>0</v>
@@ -14867,7 +14867,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T133">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451541</v>
       </c>
       <c r="U133">
         <v>0</v>
@@ -14914,7 +14914,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T134">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451541</v>
       </c>
       <c r="U134">
         <v>0</v>

--- a/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
+++ b/VerveStacks_HRV_grids_kan10/source_data/VerveStacks_HRV.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BCE4CE5-3EB7-4ECD-9ECC-BADC3007DDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F3D5488-0C9C-426D-BD3A-9E5C6B882E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="33" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="32" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="31" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="30" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="29" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="38" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="37" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="36" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="35" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="34" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1355,7 +1355,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDF0A48E-E3A2-C644-D277-9B3B3B8E5B1F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BDF59D6-FFFA-1638-3875-99B97D82AD42}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,7 +1706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F4BF8C-7A3A-4A0E-AA8A-E40EDD42D901}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11C5C21-D906-453C-8C3E-1AF0EC49035D}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4834,7 +4834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B6B2DC-7AA2-4683-93BE-8AA1E7946C22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3BAF532-F1D1-4CA3-9BA3-BE59269B2566}">
   <dimension ref="B2:L32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5899,7 +5899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B97B84-2BB9-4C43-8E2B-286EDCB0E01E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CEF9B5-4FEB-45C8-A5B0-CAC92CE2B7DE}">
   <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6378,7 +6378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858B4A8C-D1C5-4A81-B199-5A877F0BFBF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064FA59D-3388-4868-BF94-5E714618160D}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6929,7 +6929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1BD937-FFD3-4BCC-9992-276769939549}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0186A65-2408-43EB-83EF-C31F51D2FA38}">
   <dimension ref="A1:AD156"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14820,7 +14820,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T132">
-        <v>0.17225936902451541</v>
+        <v>0.17225936902451539</v>
       </c>
       <c r="U132">
         <v>0</v>
@@ -14867,7 +14867,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T133">
-        <v>0.17225936902451541</v>
+        <v>0.17225936902451539</v>
       </c>
       <c r="U133">
         <v>0</v>
@@ -14914,7 +14914,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T134">
-        <v>0.17225936902451541</v>
+        <v>0.17225936902451539</v>
       </c>
       <c r="U134">
         <v>0</v>
